--- a/languages/es/output/import/西班牙语专八精通.xlsx
+++ b/languages/es/output/import/西班牙语专八精通.xlsx
@@ -21147,7 +21147,7 @@
       </c>
       <c r="B651" s="1" t="inlineStr">
         <is>
-          <t>[peˈlado] 去皮的&lt;名&gt;</t>
+          <t>[peˈlado] 秃头的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C651" s="1" t="inlineStr">
@@ -21157,7 +21157,7 @@
       </c>
       <c r="D651" s="1" t="inlineStr">
         <is>
-          <t>去皮的</t>
+          <t>秃头的</t>
         </is>
       </c>
       <c r="E651" s="1" t="inlineStr">

--- a/languages/es/output/import/西班牙语专八精通.xlsx
+++ b/languages/es/output/import/西班牙语专八精通.xlsx
@@ -4859,7 +4859,7 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>[elˈesde] LSD&lt;名&gt;</t>
+          <t>[elˈesde] 麦角酸二乙酰胺；致幻剂LSD&lt;名&gt;</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>致幻剂LSD</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
@@ -33927,13 +33927,13 @@
       </c>
       <c r="B1053" s="1" t="inlineStr">
         <is>
-          <t>BB&lt;名&gt;</t>
+          <t>[beˈbe] 幼童；宝贝；BB弹&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1053" s="1" t="inlineStr"/>
       <c r="D1053" s="1" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>幼童</t>
         </is>
       </c>
       <c r="E1053" s="1" t="inlineStr">

--- a/languages/es/output/import/西班牙语专八精通.xlsx
+++ b/languages/es/output/import/西班牙语专八精通.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,13 +435,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>我的意思是&lt;形&gt;</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr"/>
+          <t>[[oˈse.a]] 骨的，骨质的&lt;形&gt;（“也就是说”应写作 o sea）&lt;adj&gt;</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>/oˈsea/</t>
+        </is>
+      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>我的意思是</t>
+          <t>骨的，骨质的&lt;形&gt;（“也就是说”应写作 o sea）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -658,7 +662,11 @@
           <t>不公平地&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>/inxusˈtamente/</t>
+        </is>
+      </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
           <t>不公平地</t>
@@ -715,7 +723,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>[klaˈbaɾ] 钉子&lt;动&gt;</t>
+          <t>[/klaˈbaɾ/] 钉；钉住；钉入&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -725,7 +733,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>钉子</t>
+          <t>钉；钉住；钉入</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -939,7 +947,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>[baˈsaɾ] 基地&lt;动&gt;</t>
+          <t>[/baˈsaɾ/] 以…为基础；基于&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -949,7 +957,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>基地</t>
+          <t>以…为基础；基于</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -1131,7 +1139,7 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>[malɡasˈtaɾ] 废物&lt;动&gt;</t>
+          <t>[/malɡasˈtaɾ/] 浪费；挥霍&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -1141,7 +1149,7 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>废物</t>
+          <t>浪费；挥霍</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
@@ -1198,7 +1206,11 @@
           <t>烘干机&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>/sekadˈoɾa/</t>
+        </is>
+      </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
           <t>烘干机</t>
@@ -1447,7 +1459,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>[saˈbweso] 寻血猎犬&lt;名&gt;</t>
+          <t>[/saˈbweso/] 猎犬&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1457,7 +1469,7 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>寻血猎犬</t>
+          <t>猎犬&lt;名&gt;</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -1703,13 +1715,17 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>公鸡&lt;副&gt;</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr"/>
+          <t>[[ˈpo.ʝas] 雏鸡；小母鸡&lt;adv&gt;</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>/ˈpoʝas/</t>
+        </is>
+      </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>公鸡</t>
+          <t>雏鸡；小母鸡</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -1731,7 +1747,7 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>[kasaˈnoba] 卡萨诺瓦&lt;名&gt;</t>
+          <t>[/kasaˈnoba/] 情场老手；风流男子&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1741,7 +1757,7 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>卡萨诺瓦</t>
+          <t>情场老手；风流男子&lt;名&gt;</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1987,7 +2003,7 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>[ˈtoto] 托托&lt;名&gt;</t>
+          <t>[/ˈtoto/] 托托鱼（一种鱼类）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1997,7 +2013,7 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>托托</t>
+          <t>托托鱼（一种鱼类）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -2083,7 +2099,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>[ˈlaɡteo] 乳制品&lt;名&gt;</t>
+          <t>[/ˈlaɡteo/] 乳的；乳制的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -2093,7 +2109,7 @@
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>乳制品</t>
+          <t>乳的；乳制的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -2118,7 +2134,11 @@
           <t>假设地&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr"/>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>/ipoteˈtikamente/</t>
+        </is>
+      </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
           <t>假设地</t>
@@ -2687,7 +2707,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>[ˈbat] 蝙蝠&lt;名&gt;</t>
+          <t>[/ˈbat/] 蝙蝠（英语借词；西班牙语为murciélago）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2697,7 +2717,7 @@
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>蝙蝠</t>
+          <t>蝙蝠（英语借词；西班牙语为murciélago）</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2815,7 +2835,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>[estaˈdia] 留下来&lt;名&gt;</t>
+          <t>[estaˈdia] 逗留；停留&lt;名&gt;</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2825,7 +2845,7 @@
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>留下来</t>
+          <t>逗留；停留</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -2850,7 +2870,11 @@
           <t>费德里科&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr"/>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>/fedeɾˈiko/</t>
+        </is>
+      </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
           <t>费德里科</t>
@@ -3003,7 +3027,7 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>[benˈɡala] 耀斑&lt;名&gt;</t>
+          <t>[benˈɡala] 信号弹；照明弹&lt;名&gt;</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -3013,7 +3037,7 @@
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>耀斑</t>
+          <t>信号弹；照明弹</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
@@ -3867,7 +3891,7 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>[ˈpas] 通过&lt;名&gt;</t>
+          <t>[/ˈpas/] 步子；舞步（西班牙语标准形式为 paso）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -3877,7 +3901,7 @@
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>步子；舞步（西班牙语标准形式为 paso）</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
@@ -4027,7 +4051,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>[pesˈtaɲa] 选项卡&lt;名&gt;</t>
+          <t>[/pesˈtaɲa/] 睫毛；（浏览器）选项卡&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -4037,7 +4061,7 @@
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>选项卡</t>
+          <t>睫毛；（浏览器）选项卡&lt;名&gt;</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -4763,7 +4787,7 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>[kommoˈbeɾ] 移动&lt;动&gt;</t>
+          <t>[kommoˈbeɾ] 使感动；打动&lt;动&gt;</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -4773,7 +4797,7 @@
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>移动</t>
+          <t>使感动；打动</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
@@ -4827,7 +4851,7 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>[ˈfoka] 密封件&lt;名&gt;</t>
+          <t>[ˈfoka] 海豹&lt;名&gt;</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -4837,7 +4861,7 @@
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>密封件</t>
+          <t>海豹</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
@@ -4987,7 +5011,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>[enˈfɾjaɾ] 酷&lt;动&gt;</t>
+          <t>[enˈfɾjaɾ] 使冷却；冷藏&lt;动&gt;</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -4997,7 +5021,7 @@
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>酷</t>
+          <t>使冷却；冷藏</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
@@ -5147,7 +5171,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>[oˈɾakulo] 甲骨文&lt;名&gt;</t>
+          <t>[oˈɾakulo] 神谕；神示所&lt;名&gt;</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -5157,7 +5181,7 @@
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>甲骨文</t>
+          <t>神谕；神示所</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
@@ -5499,7 +5523,7 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>[benefiˈθjaɾ] 好处&lt;动&gt;</t>
+          <t>[benefiˈθjaɾ] 使受益；有益于&lt;动&gt;</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -5509,7 +5533,7 @@
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>好处</t>
+          <t>使受益；有益于</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
@@ -5755,7 +5779,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>[tɾafiˈkaɾ] 交通&lt;动&gt;</t>
+          <t>[tɾafiˈkaɾ] 交易；做买卖；非法贩运&lt;动&gt;</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -5765,7 +5789,7 @@
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>交易；做买卖；非法贩运</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
@@ -6171,7 +6195,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>[apɾoɡsimaˈθjon] 方法&lt;名&gt;</t>
+          <t>[/apɾoɡsimaˈθjon/] 接近；近似&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -6181,7 +6205,7 @@
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>方法</t>
+          <t>接近；近似&lt;名&gt;</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
@@ -6363,7 +6387,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>[ˈlibin] 生活&lt;名&gt;</t>
+          <t>[ˈlibin] 客厅&lt;名&gt;</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -6373,7 +6397,7 @@
       </c>
       <c r="D187" s="1" t="inlineStr">
         <is>
-          <t>生活</t>
+          <t>客厅</t>
         </is>
       </c>
       <c r="E187" s="1" t="inlineStr">
@@ -6747,7 +6771,7 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>[ˈies] 是的&lt;名&gt;</t>
+          <t>[ˈies] 字母i的复数&lt;名&gt;</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
@@ -6757,7 +6781,7 @@
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>是的</t>
+          <t>字母i的复数</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
@@ -7230,7 +7254,11 @@
           <t>污垢&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C214" s="1" t="inlineStr"/>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t>/ɡɾˈime/</t>
+        </is>
+      </c>
       <c r="D214" s="1" t="inlineStr">
         <is>
           <t>污垢</t>
@@ -7575,7 +7603,7 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>[ˈθisko] 思科&lt;名&gt;</t>
+          <t>[ˈθisko] 谷壳；碎屑&lt;名&gt;</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
@@ -7585,7 +7613,7 @@
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>思科</t>
+          <t>谷壳；碎屑</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
@@ -7703,7 +7731,7 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>[ˈaɾa] 阿拉&lt;名&gt;</t>
+          <t>[ˈaɾa] 祭坛&lt;名&gt;</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
@@ -7713,7 +7741,7 @@
       </c>
       <c r="D229" s="1" t="inlineStr">
         <is>
-          <t>阿拉</t>
+          <t>祭坛</t>
         </is>
       </c>
       <c r="E229" s="1" t="inlineStr">
@@ -7962,7 +7990,11 @@
           <t>大都市的&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C237" s="1" t="inlineStr"/>
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>/metɾopolitaˈno/</t>
+        </is>
+      </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
           <t>大都市的</t>
@@ -7987,7 +8019,7 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>[poˈsaɾ] 姿势&lt;动&gt;</t>
+          <t>[poˈsaɾ] 摆姿势；（鸟）栖息；轻轻放下&lt;动&gt;</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
@@ -7997,7 +8029,7 @@
       </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
-          <t>姿势</t>
+          <t>摆姿势；（鸟）栖息；轻轻放下</t>
         </is>
       </c>
       <c r="E238" s="1" t="inlineStr">
@@ -8214,7 +8246,11 @@
           <t>无限期地&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C245" s="1" t="inlineStr"/>
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>/indefinidamenˈte/</t>
+        </is>
+      </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
           <t>无限期地</t>
@@ -8815,7 +8851,7 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>[ɡobeɾˈnante] 尺子&lt;名&gt;</t>
+          <t>[ɡobeɾˈnante] 统治者；执政者&lt;名&gt;</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
@@ -8825,7 +8861,7 @@
       </c>
       <c r="D264" s="1" t="inlineStr">
         <is>
-          <t>尺子</t>
+          <t>统治者；执政者</t>
         </is>
       </c>
       <c r="E264" s="1" t="inlineStr">
@@ -9263,7 +9299,7 @@
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>[ˈsweno] 我梦想&lt;名&gt;</t>
+          <t>[/ˈsweno/] sueño：梦；梦想&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
@@ -9273,7 +9309,7 @@
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t>我梦想</t>
+          <t>sueño：梦；梦想&lt;名&gt;</t>
         </is>
       </c>
       <c r="E278" s="1" t="inlineStr">
@@ -9423,7 +9459,7 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>[kaɾˈmelo] 卡梅尔&lt;名&gt;</t>
+          <t>[kaɾˈmelo] 焦糖；糖果&lt;名&gt;</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
@@ -9433,7 +9469,7 @@
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t>卡梅尔</t>
+          <t>焦糖；糖果</t>
         </is>
       </c>
       <c r="E283" s="1" t="inlineStr">
@@ -9551,7 +9587,7 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>[iˈθaɾ] 提升机&lt;动&gt;</t>
+          <t>[iˈθaɾ] 升起；扯起（旗帜）&lt;动&gt;</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
@@ -9561,7 +9597,7 @@
       </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
-          <t>提升机</t>
+          <t>升起；扯起（旗帜）</t>
         </is>
       </c>
       <c r="E287" s="1" t="inlineStr">
@@ -9618,7 +9654,11 @@
           <t>不被注意的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C289" s="1" t="inlineStr"/>
+      <c r="C289" s="1" t="inlineStr">
+        <is>
+          <t>/desapeɾsiˈβiðo/</t>
+        </is>
+      </c>
       <c r="D289" s="1" t="inlineStr">
         <is>
           <t>不被注意的</t>
@@ -9675,7 +9715,7 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>[paɾˈθela] 情节&lt;名&gt;</t>
+          <t>[paɾˈθela] 小块土地；地块&lt;名&gt;</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
@@ -9685,7 +9725,7 @@
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t>情节</t>
+          <t>小块土地；地块</t>
         </is>
       </c>
       <c r="E291" s="1" t="inlineStr">
@@ -9867,7 +9907,7 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>[reˈmaɾ] 行&lt;动&gt;</t>
+          <t>[reˈmaɾ] 划船；划桨&lt;动&gt;</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
@@ -9877,7 +9917,7 @@
       </c>
       <c r="D297" s="1" t="inlineStr">
         <is>
-          <t>行</t>
+          <t>划船；划桨</t>
         </is>
       </c>
       <c r="E297" s="1" t="inlineStr">
@@ -10027,7 +10067,7 @@
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t>[ˈbibɾa] 振动&lt;名&gt;</t>
+          <t>[/ˈbibɾa/] 气氛；感觉（口语，名词）；另为vibrar的第三人称单数变位&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
@@ -10037,7 +10077,7 @@
       </c>
       <c r="D302" s="1" t="inlineStr">
         <is>
-          <t>振动</t>
+          <t>气氛；感觉（口语，名词）；另为vibrar的第三人称单数变位</t>
         </is>
       </c>
       <c r="E302" s="1" t="inlineStr">
@@ -10347,7 +10387,7 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>[oɾdeˈnando] 订购&lt;名&gt;</t>
+          <t>[/oɾdeˈnando/] ordenar的现在分词（整理；订购）&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
@@ -10357,7 +10397,7 @@
       </c>
       <c r="D312" s="1" t="inlineStr">
         <is>
-          <t>订购</t>
+          <t>ordenar的现在分词（整理；订购）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E312" s="1" t="inlineStr">
@@ -10635,7 +10675,7 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>[inˈfante] 婴儿&lt;名&gt;</t>
+          <t>[/inˈfante/] 儿童；王子&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
@@ -10645,7 +10685,7 @@
       </c>
       <c r="D321" s="1" t="inlineStr">
         <is>
-          <t>婴儿</t>
+          <t>儿童；王子&lt;名&gt;</t>
         </is>
       </c>
       <c r="E321" s="1" t="inlineStr">
@@ -10862,7 +10902,11 @@
           <t>可汗&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C328" s="1" t="inlineStr"/>
+      <c r="C328" s="1" t="inlineStr">
+        <is>
+          <t>/kan/</t>
+        </is>
+      </c>
       <c r="D328" s="1" t="inlineStr">
         <is>
           <t>可汗</t>
@@ -10890,7 +10934,11 @@
           <t>不可数的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C329" s="1" t="inlineStr"/>
+      <c r="C329" s="1" t="inlineStr">
+        <is>
+          <t>/iŋkontaβle/</t>
+        </is>
+      </c>
       <c r="D329" s="1" t="inlineStr">
         <is>
           <t>不可数的</t>
@@ -10915,7 +10963,7 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>[ˈfunebɾe] 葬礼&lt;形&gt;</t>
+          <t>[ˈfunebɾe] 葬礼的；悲哀的；阴森的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr">
@@ -10925,7 +10973,7 @@
       </c>
       <c r="D330" s="1" t="inlineStr">
         <is>
-          <t>葬礼</t>
+          <t>葬礼的；悲哀的；阴森的</t>
         </is>
       </c>
       <c r="E330" s="1" t="inlineStr">
@@ -11171,7 +11219,7 @@
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡɾiʝo] 板球&lt;名&gt;</t>
+          <t>[ˈɡɾiʝo] 蟋蟀&lt;名&gt;</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
@@ -11181,7 +11229,7 @@
       </c>
       <c r="D338" s="1" t="inlineStr">
         <is>
-          <t>板球</t>
+          <t>蟋蟀</t>
         </is>
       </c>
       <c r="E338" s="1" t="inlineStr">
@@ -11619,7 +11667,7 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t>[moˈxaɾ] 湿的&lt;动&gt;</t>
+          <t>[moˈxaɾ] 弄湿；浸湿&lt;动&gt;</t>
         </is>
       </c>
       <c r="C352" s="1" t="inlineStr">
@@ -11629,7 +11677,7 @@
       </c>
       <c r="D352" s="1" t="inlineStr">
         <is>
-          <t>湿的</t>
+          <t>弄湿；浸湿</t>
         </is>
       </c>
       <c r="E352" s="1" t="inlineStr">
@@ -11750,7 +11798,11 @@
           <t>塞尔达&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C356" s="1" t="inlineStr"/>
+      <c r="C356" s="1" t="inlineStr">
+        <is>
+          <t>/θˈelda/</t>
+        </is>
+      </c>
       <c r="D356" s="1" t="inlineStr">
         <is>
           <t>塞尔达</t>
@@ -11999,7 +12051,7 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>[desliˈθaɾ] 幻灯片&lt;动&gt;</t>
+          <t>[desliˈθaɾ] 滑动；滑行；滑落&lt;动&gt;</t>
         </is>
       </c>
       <c r="C364" s="1" t="inlineStr">
@@ -12009,7 +12061,7 @@
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t>幻灯片</t>
+          <t>滑动；滑行；滑落</t>
         </is>
       </c>
       <c r="E364" s="1" t="inlineStr">
@@ -12159,7 +12211,7 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t>[deletɾeˈaɾ] 咒语&lt;动&gt;</t>
+          <t>[deletɾeˈaɾ] 拼写；逐字母拼读&lt;动&gt;</t>
         </is>
       </c>
       <c r="C369" s="1" t="inlineStr">
@@ -12169,7 +12221,7 @@
       </c>
       <c r="D369" s="1" t="inlineStr">
         <is>
-          <t>咒语</t>
+          <t>拼写；逐字母拼读</t>
         </is>
       </c>
       <c r="E369" s="1" t="inlineStr">
@@ -12479,7 +12531,7 @@
       </c>
       <c r="B379" s="1" t="inlineStr">
         <is>
-          <t>[ˈoɡsido] 生锈&lt;名&gt;</t>
+          <t>[ˈoɡsido] 锈；氧化物&lt;名&gt;</t>
         </is>
       </c>
       <c r="C379" s="1" t="inlineStr">
@@ -12489,7 +12541,7 @@
       </c>
       <c r="D379" s="1" t="inlineStr">
         <is>
-          <t>生锈</t>
+          <t>锈；氧化物</t>
         </is>
       </c>
       <c r="E379" s="1" t="inlineStr">
@@ -12607,7 +12659,7 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>[ˈmeiʝoɾ] 专业&lt;名&gt;</t>
+          <t>[ˈmeiʝoɾ] 更好的；较好的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C383" s="1" t="inlineStr">
@@ -12617,7 +12669,7 @@
       </c>
       <c r="D383" s="1" t="inlineStr">
         <is>
-          <t>专业</t>
+          <t>更好的；较好的</t>
         </is>
       </c>
       <c r="E383" s="1" t="inlineStr">
@@ -12671,7 +12723,7 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>[ˈlama] 喇嘛&lt;名&gt;</t>
+          <t>[/ˈlama/] 喇嘛&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C385" s="1" t="inlineStr">
@@ -12738,7 +12790,11 @@
           <t>毫无疑问&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C387" s="1" t="inlineStr"/>
+      <c r="C387" s="1" t="inlineStr">
+        <is>
+          <t>/induˌðaβleˈmente/</t>
+        </is>
+      </c>
       <c r="D387" s="1" t="inlineStr">
         <is>
           <t>毫无疑问</t>
@@ -13051,7 +13107,7 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t>[silˈbido] 口哨&lt;名&gt;</t>
+          <t>[/silˈbido/] 哨声；口哨声&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C397" s="1" t="inlineStr">
@@ -13061,7 +13117,7 @@
       </c>
       <c r="D397" s="1" t="inlineStr">
         <is>
-          <t>口哨</t>
+          <t>哨声；口哨声&lt;名&gt;</t>
         </is>
       </c>
       <c r="E397" s="1" t="inlineStr">
@@ -13179,7 +13235,7 @@
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t>[ˈbaina] 吊舱&lt;名&gt;</t>
+          <t>[ˈbaina] 豆荚；鞘；套&lt;名&gt;</t>
         </is>
       </c>
       <c r="C401" s="1" t="inlineStr">
@@ -13189,7 +13245,7 @@
       </c>
       <c r="D401" s="1" t="inlineStr">
         <is>
-          <t>吊舱</t>
+          <t>豆荚；鞘；套</t>
         </is>
       </c>
       <c r="E401" s="1" t="inlineStr">
@@ -13435,13 +13491,17 @@
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t>马里布&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C409" s="1" t="inlineStr"/>
+          <t>[[ma.liˈβu]] 马利宝椰子朗姆酒&lt;名&gt;&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C409" s="1" t="inlineStr">
+        <is>
+          <t>/malibˈu/</t>
+        </is>
+      </c>
       <c r="D409" s="1" t="inlineStr">
         <is>
-          <t>马里布</t>
+          <t>马利宝椰子朗姆酒&lt;名&gt;</t>
         </is>
       </c>
       <c r="E409" s="1" t="inlineStr">
@@ -13498,7 +13558,11 @@
           <t>护林员&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C411" s="1" t="inlineStr"/>
+      <c r="C411" s="1" t="inlineStr">
+        <is>
+          <t>/ɡwaɾðaˈboskes/</t>
+        </is>
+      </c>
       <c r="D411" s="1" t="inlineStr">
         <is>
           <t>护林员</t>
@@ -13555,7 +13619,7 @@
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t>[ˈambaɾ] 琥珀色&lt;名&gt;</t>
+          <t>[/ˈambaɾ/] 琥珀；琥珀色&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C413" s="1" t="inlineStr">
@@ -13565,7 +13629,7 @@
       </c>
       <c r="D413" s="1" t="inlineStr">
         <is>
-          <t>琥珀色</t>
+          <t>琥珀；琥珀色&lt;名&gt;</t>
         </is>
       </c>
       <c r="E413" s="1" t="inlineStr">
@@ -13683,7 +13747,7 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>[opeˈɾado] 经营的&lt;形&gt;</t>
+          <t>[opeˈɾado] 动过手术的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C417" s="1" t="inlineStr">
@@ -13693,7 +13757,7 @@
       </c>
       <c r="D417" s="1" t="inlineStr">
         <is>
-          <t>经营的</t>
+          <t>动过手术的</t>
         </is>
       </c>
       <c r="E417" s="1" t="inlineStr">
@@ -13715,7 +13779,7 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>[ˈsub] 子&lt;介&gt;</t>
+          <t>[ˈsub] 在下；低于；亚；次&lt;介&gt;</t>
         </is>
       </c>
       <c r="C418" s="1" t="inlineStr">
@@ -13725,7 +13789,7 @@
       </c>
       <c r="D418" s="1" t="inlineStr">
         <is>
-          <t>子</t>
+          <t>在下；低于；亚；次</t>
         </is>
       </c>
       <c r="E418" s="1" t="inlineStr">
@@ -13878,7 +13942,11 @@
           <t>托莱多&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C423" s="1" t="inlineStr"/>
+      <c r="C423" s="1" t="inlineStr">
+        <is>
+          <t>/toleðo/</t>
+        </is>
+      </c>
       <c r="D423" s="1" t="inlineStr">
         <is>
           <t>托莱多</t>
@@ -13903,7 +13971,7 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>[moˈnada] 可爱&lt;名&gt;</t>
+          <t>[/moˈnada/] 可爱的东西&lt;名&gt;；鬼脸&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C424" s="1" t="inlineStr">
@@ -13913,7 +13981,7 @@
       </c>
       <c r="D424" s="1" t="inlineStr">
         <is>
-          <t>可爱</t>
+          <t>可爱的东西&lt;名&gt;；鬼脸&lt;名&gt;</t>
         </is>
       </c>
       <c r="E424" s="1" t="inlineStr">
@@ -14386,7 +14454,11 @@
           <t>安定&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C439" s="1" t="inlineStr"/>
+      <c r="C439" s="1" t="inlineStr">
+        <is>
+          <t>/baliˈum/</t>
+        </is>
+      </c>
       <c r="D439" s="1" t="inlineStr">
         <is>
           <t>安定</t>
@@ -14411,7 +14483,7 @@
       </c>
       <c r="B440" s="1" t="inlineStr">
         <is>
-          <t>[laɡɾiˈmaɾ] 眼泪&lt;动&gt;</t>
+          <t>[laɡɾiˈmaɾ] 流泪；哭泣&lt;动&gt;</t>
         </is>
       </c>
       <c r="C440" s="1" t="inlineStr">
@@ -14421,7 +14493,7 @@
       </c>
       <c r="D440" s="1" t="inlineStr">
         <is>
-          <t>眼泪</t>
+          <t>流泪；哭泣</t>
         </is>
       </c>
       <c r="E440" s="1" t="inlineStr">
@@ -14571,7 +14643,7 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t>[rekosˈtaɾ] 躺下&lt;动&gt;</t>
+          <t>[/rekosˈtaɾ/] 使躺下；使斜倚（recostarse 躺下）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C445" s="1" t="inlineStr">
@@ -14581,7 +14653,7 @@
       </c>
       <c r="D445" s="1" t="inlineStr">
         <is>
-          <t>躺下</t>
+          <t>使躺下；使斜倚（recostarse 躺下）</t>
         </is>
       </c>
       <c r="E445" s="1" t="inlineStr">
@@ -14667,7 +14739,7 @@
       </c>
       <c r="B448" s="1" t="inlineStr">
         <is>
-          <t>[inˈflwiɾ] 影响力&lt;动&gt;</t>
+          <t>[inˈflwiɾ] 影响&lt;动&gt;</t>
         </is>
       </c>
       <c r="C448" s="1" t="inlineStr">
@@ -14677,7 +14749,7 @@
       </c>
       <c r="D448" s="1" t="inlineStr">
         <is>
-          <t>影响力</t>
+          <t>影响</t>
         </is>
       </c>
       <c r="E448" s="1" t="inlineStr">
@@ -14987,7 +15059,7 @@
       </c>
       <c r="B458" s="1" t="inlineStr">
         <is>
-          <t>[esˈtela] 醒来&lt;名&gt;</t>
+          <t>[esˈtela] 航迹；尾流；石碑&lt;名&gt;</t>
         </is>
       </c>
       <c r="C458" s="1" t="inlineStr">
@@ -14997,7 +15069,7 @@
       </c>
       <c r="D458" s="1" t="inlineStr">
         <is>
-          <t>醒来</t>
+          <t>航迹；尾流；石碑</t>
         </is>
       </c>
       <c r="E458" s="1" t="inlineStr">
@@ -15179,7 +15251,7 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t>[ˈfaθe] 脸&lt;名&gt;</t>
+          <t>[/ˈfaθe/] 做；干；……以前&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C464" s="1" t="inlineStr">
@@ -15189,7 +15261,7 @@
       </c>
       <c r="D464" s="1" t="inlineStr">
         <is>
-          <t>脸</t>
+          <t>做；干；……以前</t>
         </is>
       </c>
       <c r="E464" s="1" t="inlineStr">
@@ -15211,7 +15283,7 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>[funˈdaɾ] 发现&lt;动&gt;</t>
+          <t>[funˈdaɾ] 创立；建立；创办&lt;动&gt;</t>
         </is>
       </c>
       <c r="C465" s="1" t="inlineStr">
@@ -15221,7 +15293,7 @@
       </c>
       <c r="D465" s="1" t="inlineStr">
         <is>
-          <t>发现</t>
+          <t>创立；建立；创办</t>
         </is>
       </c>
       <c r="E465" s="1" t="inlineStr">
@@ -15243,7 +15315,7 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>[imˈbalido] 无效&lt;形&gt;</t>
+          <t>[/imˈbalido/] 残疾的；病弱的&lt;形&gt;；残疾人&lt;名&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C466" s="1" t="inlineStr">
@@ -15253,7 +15325,7 @@
       </c>
       <c r="D466" s="1" t="inlineStr">
         <is>
-          <t>无效</t>
+          <t>残疾的；病弱的&lt;形&gt;；残疾人&lt;名&gt;</t>
         </is>
       </c>
       <c r="E466" s="1" t="inlineStr">
@@ -15435,7 +15507,7 @@
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡɾas] 格拉斯&lt;名&gt;</t>
+          <t>[/ˈɡɾas/] 肥的；脂肪&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C472" s="1" t="inlineStr">
@@ -15445,7 +15517,7 @@
       </c>
       <c r="D472" s="1" t="inlineStr">
         <is>
-          <t>格拉斯</t>
+          <t>肥的；脂肪</t>
         </is>
       </c>
       <c r="E472" s="1" t="inlineStr">
@@ -15531,7 +15603,7 @@
       </c>
       <c r="B475" s="1" t="inlineStr">
         <is>
-          <t>[fundaˈmento] 基金会&lt;名&gt;</t>
+          <t>[fundaˈmento] 基础；根据；理由&lt;名&gt;</t>
         </is>
       </c>
       <c r="C475" s="1" t="inlineStr">
@@ -15541,7 +15613,7 @@
       </c>
       <c r="D475" s="1" t="inlineStr">
         <is>
-          <t>基金会</t>
+          <t>基础；根据；理由</t>
         </is>
       </c>
       <c r="E475" s="1" t="inlineStr">
@@ -16459,7 +16531,7 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>[ˈt͡ʃoro] 喷射机&lt;名&gt;</t>
+          <t>[ˈt͡ʃoro] 一股（液体）；喷流；射流&lt;名&gt;</t>
         </is>
       </c>
       <c r="C504" s="1" t="inlineStr">
@@ -16469,7 +16541,7 @@
       </c>
       <c r="D504" s="1" t="inlineStr">
         <is>
-          <t>喷射机</t>
+          <t>一股（液体）；喷流；射流</t>
         </is>
       </c>
       <c r="E504" s="1" t="inlineStr">
@@ -16715,7 +16787,7 @@
       </c>
       <c r="B512" s="1" t="inlineStr">
         <is>
-          <t>[eneɾˈxetika] 能量&lt;名&gt;</t>
+          <t>[eneɾˈxetika] 能量的；精力的；能源业&lt;名&gt;</t>
         </is>
       </c>
       <c r="C512" s="1" t="inlineStr">
@@ -16725,7 +16797,7 @@
       </c>
       <c r="D512" s="1" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>能量的；精力的；能源业</t>
         </is>
       </c>
       <c r="E512" s="1" t="inlineStr">
@@ -16811,7 +16883,7 @@
       </c>
       <c r="B515" s="1" t="inlineStr">
         <is>
-          <t>[diˈbeɾso] 多样化&lt;形&gt;</t>
+          <t>[/diˈbeɾso/] 多样的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C515" s="1" t="inlineStr">
@@ -16821,7 +16893,7 @@
       </c>
       <c r="D515" s="1" t="inlineStr">
         <is>
-          <t>多样化</t>
+          <t>多样的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E515" s="1" t="inlineStr">
@@ -17099,7 +17171,7 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>[bombaɾdeˈaɾ] 炸弹&lt;动&gt;</t>
+          <t>[bombaɾdeˈaɾ] 轰炸；炮轰&lt;动&gt;</t>
         </is>
       </c>
       <c r="C524" s="1" t="inlineStr">
@@ -17109,7 +17181,7 @@
       </c>
       <c r="D524" s="1" t="inlineStr">
         <is>
-          <t>炸弹</t>
+          <t>轰炸；炮轰</t>
         </is>
       </c>
       <c r="E524" s="1" t="inlineStr">
@@ -17515,7 +17587,7 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>[oɾaˈdoɾ] 扬声器&lt;名&gt;</t>
+          <t>[oɾaˈdoɾ] 演讲者；演说家&lt;名&gt;</t>
         </is>
       </c>
       <c r="C537" s="1" t="inlineStr">
@@ -17525,7 +17597,7 @@
       </c>
       <c r="D537" s="1" t="inlineStr">
         <is>
-          <t>扬声器</t>
+          <t>演讲者；演说家</t>
         </is>
       </c>
       <c r="E537" s="1" t="inlineStr">
@@ -17803,7 +17875,7 @@
       </c>
       <c r="B546" s="1" t="inlineStr">
         <is>
-          <t>[mananˈtjal] 春天&lt;名&gt;</t>
+          <t>[mananˈtjal] 泉；泉源；源泉&lt;名&gt;</t>
         </is>
       </c>
       <c r="C546" s="1" t="inlineStr">
@@ -17813,7 +17885,7 @@
       </c>
       <c r="D546" s="1" t="inlineStr">
         <is>
-          <t>春天</t>
+          <t>泉；泉源；源泉</t>
         </is>
       </c>
       <c r="E546" s="1" t="inlineStr">
@@ -17963,7 +18035,7 @@
       </c>
       <c r="B551" s="1" t="inlineStr">
         <is>
-          <t>[bolaˈdoɾa] 飞行&lt;名&gt;</t>
+          <t>[/bolaˈdoɾa/] 会飞的（阴性）&lt;形&gt;；飞刀&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C551" s="1" t="inlineStr">
@@ -17973,7 +18045,7 @@
       </c>
       <c r="D551" s="1" t="inlineStr">
         <is>
-          <t>飞行</t>
+          <t>会飞的（阴性）&lt;形&gt;；飞刀&lt;名&gt;</t>
         </is>
       </c>
       <c r="E551" s="1" t="inlineStr">
@@ -18030,7 +18102,11 @@
           <t>韦伯&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C553" s="1" t="inlineStr"/>
+      <c r="C553" s="1" t="inlineStr">
+        <is>
+          <t>/webˈeɾ/</t>
+        </is>
+      </c>
       <c r="D553" s="1" t="inlineStr">
         <is>
           <t>韦伯</t>
@@ -18090,7 +18166,11 @@
           <t>交流电&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C555" s="1" t="inlineStr"/>
+      <c r="C555" s="1" t="inlineStr">
+        <is>
+          <t>/ˈaθ/</t>
+        </is>
+      </c>
       <c r="D555" s="1" t="inlineStr">
         <is>
           <t>交流电</t>
@@ -18147,7 +18227,7 @@
       </c>
       <c r="B557" s="1" t="inlineStr">
         <is>
-          <t>[ˈbaʝo] 湾&lt;名&gt;</t>
+          <t>[ˈbaʝo] 浅黄褐色的马；浅黄褐色（马毛色）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C557" s="1" t="inlineStr">
@@ -18157,7 +18237,7 @@
       </c>
       <c r="D557" s="1" t="inlineStr">
         <is>
-          <t>湾</t>
+          <t>浅黄褐色的马；浅黄褐色（马毛色）</t>
         </is>
       </c>
       <c r="E557" s="1" t="inlineStr">
@@ -18630,7 +18710,11 @@
           <t>巴比伦的&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C572" s="1" t="inlineStr"/>
+      <c r="C572" s="1" t="inlineStr">
+        <is>
+          <t>/baβilonjo/</t>
+        </is>
+      </c>
       <c r="D572" s="1" t="inlineStr">
         <is>
           <t>巴比伦的</t>
@@ -18687,7 +18771,7 @@
       </c>
       <c r="B574" s="1" t="inlineStr">
         <is>
-          <t>[ˈpixa] 豪华&lt;名&gt;</t>
+          <t>[ˈpixa] 富家小姐；势利眼；睡裙&lt;名&gt;</t>
         </is>
       </c>
       <c r="C574" s="1" t="inlineStr">
@@ -18697,7 +18781,7 @@
       </c>
       <c r="D574" s="1" t="inlineStr">
         <is>
-          <t>豪华</t>
+          <t>富家小姐；势利眼；睡裙</t>
         </is>
       </c>
       <c r="E574" s="1" t="inlineStr">
@@ -18783,7 +18867,7 @@
       </c>
       <c r="B577" s="1" t="inlineStr">
         <is>
-          <t>[relaˈtibo] 亲戚&lt;形&gt;</t>
+          <t>[relaˈtibo] 相对的；与…有关的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C577" s="1" t="inlineStr">
@@ -18793,7 +18877,7 @@
       </c>
       <c r="D577" s="1" t="inlineStr">
         <is>
-          <t>亲戚</t>
+          <t>相对的；与…有关的</t>
         </is>
       </c>
       <c r="E577" s="1" t="inlineStr">
@@ -18975,7 +19059,7 @@
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
-          <t>[apɾobeˈt͡ʃado] 被利用&lt;形&gt;</t>
+          <t>[apɾobeˈt͡ʃado] 投机取巧的；爱占便宜的；勤奋好学的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C583" s="1" t="inlineStr">
@@ -18985,7 +19069,7 @@
       </c>
       <c r="D583" s="1" t="inlineStr">
         <is>
-          <t>被利用</t>
+          <t>投机取巧的；爱占便宜的；勤奋好学的</t>
         </is>
       </c>
       <c r="E583" s="1" t="inlineStr">
@@ -19042,7 +19126,11 @@
           <t>痴迷的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C585" s="1" t="inlineStr"/>
+      <c r="C585" s="1" t="inlineStr">
+        <is>
+          <t>/oβsesiβo/</t>
+        </is>
+      </c>
       <c r="D585" s="1" t="inlineStr">
         <is>
           <t>痴迷的</t>
@@ -19131,7 +19219,7 @@
       </c>
       <c r="B588" s="1" t="inlineStr">
         <is>
-          <t>[ˈpin] 针&lt;名&gt;</t>
+          <t>[/ˈpin/] 大头针&lt;名&gt;；图钉&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C588" s="1" t="inlineStr">
@@ -19141,7 +19229,7 @@
       </c>
       <c r="D588" s="1" t="inlineStr">
         <is>
-          <t>针</t>
+          <t>大头针&lt;名&gt;；图钉&lt;名&gt;</t>
         </is>
       </c>
       <c r="E588" s="1" t="inlineStr">
@@ -19771,7 +19859,7 @@
       </c>
       <c r="B608" s="1" t="inlineStr">
         <is>
-          <t>[aˈxeno] 外星人&lt;形&gt;</t>
+          <t>[/aˈxeno/] 别人的；外来的；陌生的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C608" s="1" t="inlineStr">
@@ -19781,7 +19869,7 @@
       </c>
       <c r="D608" s="1" t="inlineStr">
         <is>
-          <t>外星人</t>
+          <t>别人的；外来的；陌生的</t>
         </is>
       </c>
       <c r="E608" s="1" t="inlineStr">
@@ -20091,7 +20179,7 @@
       </c>
       <c r="B618" s="1" t="inlineStr">
         <is>
-          <t>[ˈpodɾe] 我会腐烂&lt;名&gt;</t>
+          <t>[/ˈpodɾe/] 腐烂的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C618" s="1" t="inlineStr">
@@ -20101,7 +20189,7 @@
       </c>
       <c r="D618" s="1" t="inlineStr">
         <is>
-          <t>我会腐烂</t>
+          <t>腐烂的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E618" s="1" t="inlineStr">
@@ -20123,7 +20211,7 @@
       </c>
       <c r="B619" s="1" t="inlineStr">
         <is>
-          <t>[neˈbaɾ] 雪&lt;动&gt;</t>
+          <t>[/neˈbaɾ/] 下雪&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C619" s="1" t="inlineStr">
@@ -20133,7 +20221,7 @@
       </c>
       <c r="D619" s="1" t="inlineStr">
         <is>
-          <t>雪</t>
+          <t>下雪</t>
         </is>
       </c>
       <c r="E619" s="1" t="inlineStr">
@@ -20155,7 +20243,7 @@
       </c>
       <c r="B620" s="1" t="inlineStr">
         <is>
-          <t>[ˈsi] 希&lt;名&gt;</t>
+          <t>[/ˈsi/] 希腊字母ξ&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C620" s="1" t="inlineStr">
@@ -20165,7 +20253,7 @@
       </c>
       <c r="D620" s="1" t="inlineStr">
         <is>
-          <t>希</t>
+          <t>希腊字母ξ&lt;名&gt;</t>
         </is>
       </c>
       <c r="E620" s="1" t="inlineStr">
@@ -20251,7 +20339,7 @@
       </c>
       <c r="B623" s="1" t="inlineStr">
         <is>
-          <t>[kantiˈneɾo] 调酒师&lt;名&gt;</t>
+          <t>[/kantiˈneɾo/] 酒保，小酒馆老板&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C623" s="1" t="inlineStr">
@@ -20261,7 +20349,7 @@
       </c>
       <c r="D623" s="1" t="inlineStr">
         <is>
-          <t>调酒师</t>
+          <t>酒保，小酒馆老板&lt;名&gt;</t>
         </is>
       </c>
       <c r="E623" s="1" t="inlineStr">
@@ -20667,7 +20755,7 @@
       </c>
       <c r="B636" s="1" t="inlineStr">
         <is>
-          <t>[infɾaˈmundo] 黑社会&lt;名&gt;</t>
+          <t>[/infɾaˈmundo/] 阴间；冥界；地下世界&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C636" s="1" t="inlineStr">
@@ -20677,7 +20765,7 @@
       </c>
       <c r="D636" s="1" t="inlineStr">
         <is>
-          <t>黑社会</t>
+          <t>阴间；冥界；地下世界</t>
         </is>
       </c>
       <c r="E636" s="1" t="inlineStr">
@@ -20731,7 +20819,7 @@
       </c>
       <c r="B638" s="1" t="inlineStr">
         <is>
-          <t>[fideikoˈmiso] 信任&lt;名&gt;</t>
+          <t>[/fideikoˈmiso/] 信托&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C638" s="1" t="inlineStr">
@@ -20741,7 +20829,7 @@
       </c>
       <c r="D638" s="1" t="inlineStr">
         <is>
-          <t>信任</t>
+          <t>信托</t>
         </is>
       </c>
       <c r="E638" s="1" t="inlineStr">
@@ -21115,7 +21203,7 @@
       </c>
       <c r="B650" s="1" t="inlineStr">
         <is>
-          <t>[ˈsim] 辛&lt;名&gt;</t>
+          <t>[/ˈsim/] SIM卡&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C650" s="1" t="inlineStr">
@@ -21125,7 +21213,7 @@
       </c>
       <c r="D650" s="1" t="inlineStr">
         <is>
-          <t>辛</t>
+          <t>SIM卡</t>
         </is>
       </c>
       <c r="E650" s="1" t="inlineStr">
@@ -21243,13 +21331,17 @@
       </c>
       <c r="B654" s="1" t="inlineStr">
         <is>
-          <t>在&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C654" s="1" t="inlineStr"/>
+          <t>[[pulx] 英寸&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C654" s="1" t="inlineStr">
+        <is>
+          <t>/pˈulx/</t>
+        </is>
+      </c>
       <c r="D654" s="1" t="inlineStr">
         <is>
-          <t>在</t>
+          <t>英寸</t>
         </is>
       </c>
       <c r="E654" s="1" t="inlineStr">
@@ -21431,7 +21523,7 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>[ˈlidja] 利迪亚&lt;名&gt;</t>
+          <t>[/ˈlidja/] 斗牛；对付；处理&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C660" s="1" t="inlineStr">
@@ -21441,7 +21533,7 @@
       </c>
       <c r="D660" s="1" t="inlineStr">
         <is>
-          <t>利迪亚</t>
+          <t>斗牛；对付；处理</t>
         </is>
       </c>
       <c r="E660" s="1" t="inlineStr">
@@ -21466,7 +21558,11 @@
           <t>蜘蛛&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C661" s="1" t="inlineStr"/>
+      <c r="C661" s="1" t="inlineStr">
+        <is>
+          <t>/spidˈeɾ/</t>
+        </is>
+      </c>
       <c r="D661" s="1" t="inlineStr">
         <is>
           <t>蜘蛛</t>
@@ -21491,7 +21587,7 @@
       </c>
       <c r="B662" s="1" t="inlineStr">
         <is>
-          <t>[aɾaˈɲaθo] 从头开始&lt;名&gt;</t>
+          <t>[/aɾaˈɲaθo/] 抓伤；抓痕；划痕&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C662" s="1" t="inlineStr">
@@ -21501,7 +21597,7 @@
       </c>
       <c r="D662" s="1" t="inlineStr">
         <is>
-          <t>从头开始</t>
+          <t>抓伤；抓痕；划痕</t>
         </is>
       </c>
       <c r="E662" s="1" t="inlineStr">
@@ -21622,7 +21718,11 @@
           <t>引人注目的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C666" s="1" t="inlineStr"/>
+      <c r="C666" s="1" t="inlineStr">
+        <is>
+          <t>/ʎamatiβo/</t>
+        </is>
+      </c>
       <c r="D666" s="1" t="inlineStr">
         <is>
           <t>引人注目的</t>
@@ -21650,7 +21750,11 @@
           <t>粘性的&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C667" s="1" t="inlineStr"/>
+      <c r="C667" s="1" t="inlineStr">
+        <is>
+          <t>/peɣaxosa/</t>
+        </is>
+      </c>
       <c r="D667" s="1" t="inlineStr">
         <is>
           <t>粘性的</t>
@@ -22094,7 +22198,11 @@
           <t>骑师&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C681" s="1" t="inlineStr"/>
+      <c r="C681" s="1" t="inlineStr">
+        <is>
+          <t>/xokkˈej/</t>
+        </is>
+      </c>
       <c r="D681" s="1" t="inlineStr">
         <is>
           <t>骑师</t>
@@ -22122,7 +22230,11 @@
           <t>付钱&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C682" s="1" t="inlineStr"/>
+      <c r="C682" s="1" t="inlineStr">
+        <is>
+          <t>/paɣaɾla/</t>
+        </is>
+      </c>
       <c r="D682" s="1" t="inlineStr">
         <is>
           <t>付钱</t>
@@ -22886,7 +22998,11 @@
           <t>超声波&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C706" s="1" t="inlineStr"/>
+      <c r="C706" s="1" t="inlineStr">
+        <is>
+          <t>/ultɾasoˈnido/</t>
+        </is>
+      </c>
       <c r="D706" s="1" t="inlineStr">
         <is>
           <t>超声波</t>
@@ -23007,7 +23123,7 @@
       </c>
       <c r="B710" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡoɾe] 戈尔&lt;名&gt;</t>
+          <t>[/ˈɡoɾe/] 血腥；血腥暴力（影视题材）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C710" s="1" t="inlineStr">
@@ -23017,7 +23133,7 @@
       </c>
       <c r="D710" s="1" t="inlineStr">
         <is>
-          <t>戈尔</t>
+          <t>血腥；血腥暴力（影视题材）</t>
         </is>
       </c>
       <c r="E710" s="1" t="inlineStr">
@@ -23135,7 +23251,7 @@
       </c>
       <c r="B714" s="1" t="inlineStr">
         <is>
-          <t>[kɾaneˈal] 颅骨&lt;形&gt;</t>
+          <t>[/kɾaneˈal/] 颅的；颅骨的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C714" s="1" t="inlineStr">
@@ -23145,7 +23261,7 @@
       </c>
       <c r="D714" s="1" t="inlineStr">
         <is>
-          <t>颅骨</t>
+          <t>颅的；颅骨的</t>
         </is>
       </c>
       <c r="E714" s="1" t="inlineStr">
@@ -23967,7 +24083,7 @@
       </c>
       <c r="B740" s="1" t="inlineStr">
         <is>
-          <t>[kapaɾaˈθon] 外壳&lt;名&gt;</t>
+          <t>[/kapaɾaˈθon/] 甲壳（龟、蟹等的硬壳）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C740" s="1" t="inlineStr">
@@ -23977,7 +24093,7 @@
       </c>
       <c r="D740" s="1" t="inlineStr">
         <is>
-          <t>外壳</t>
+          <t>甲壳（龟、蟹等的硬壳）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E740" s="1" t="inlineStr">
@@ -24063,7 +24179,7 @@
       </c>
       <c r="B743" s="1" t="inlineStr">
         <is>
-          <t>[floɾeˈθeɾ] 蓬勃发展&lt;动&gt;</t>
+          <t>[/floɾeˈθeɾ/] 开花；繁荣，蓬勃发展&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C743" s="1" t="inlineStr">
@@ -24073,7 +24189,7 @@
       </c>
       <c r="D743" s="1" t="inlineStr">
         <is>
-          <t>蓬勃发展</t>
+          <t>开花；繁荣，蓬勃发展&lt;动&gt;</t>
         </is>
       </c>
       <c r="E743" s="1" t="inlineStr">
@@ -24290,7 +24406,11 @@
           <t>士官&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C750" s="1" t="inlineStr"/>
+      <c r="C750" s="1" t="inlineStr">
+        <is>
+          <t>/subofiˈθjal/</t>
+        </is>
+      </c>
       <c r="D750" s="1" t="inlineStr">
         <is>
           <t>士官</t>
@@ -24507,7 +24627,7 @@
       </c>
       <c r="B757" s="1" t="inlineStr">
         <is>
-          <t>[aˈtasko] 果酱&lt;名&gt;</t>
+          <t>[/aˈtasko/] 堵车；交通堵塞；堵塞&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C757" s="1" t="inlineStr">
@@ -24517,7 +24637,7 @@
       </c>
       <c r="D757" s="1" t="inlineStr">
         <is>
-          <t>果酱</t>
+          <t>堵车；交通堵塞；堵塞</t>
         </is>
       </c>
       <c r="E757" s="1" t="inlineStr">
@@ -24670,7 +24790,11 @@
           <t>突袭&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C762" s="1" t="inlineStr"/>
+      <c r="C762" s="1" t="inlineStr">
+        <is>
+          <t>/inkuɾˈsjon/</t>
+        </is>
+      </c>
       <c r="D762" s="1" t="inlineStr">
         <is>
           <t>突袭</t>
@@ -24730,7 +24854,11 @@
           <t>便便&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C764" s="1" t="inlineStr"/>
+      <c r="C764" s="1" t="inlineStr">
+        <is>
+          <t>/poˈpo/</t>
+        </is>
+      </c>
       <c r="D764" s="1" t="inlineStr">
         <is>
           <t>便便</t>
@@ -24787,7 +24915,7 @@
       </c>
       <c r="B766" s="1" t="inlineStr">
         <is>
-          <t>[nombɾaˈmjento] 预约&lt;名&gt;</t>
+          <t>[/nombɾaˈmjento/] 任命；委任；任命书&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C766" s="1" t="inlineStr">
@@ -24797,7 +24925,7 @@
       </c>
       <c r="D766" s="1" t="inlineStr">
         <is>
-          <t>预约</t>
+          <t>任命；委任；任命书</t>
         </is>
       </c>
       <c r="E766" s="1" t="inlineStr">
@@ -24819,7 +24947,7 @@
       </c>
       <c r="B767" s="1" t="inlineStr">
         <is>
-          <t>[aɾboˈlaɾ] 树&lt;动&gt;</t>
+          <t>[/aɾboˈlaɾ/] 升起；竖起&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C767" s="1" t="inlineStr">
@@ -24829,7 +24957,7 @@
       </c>
       <c r="D767" s="1" t="inlineStr">
         <is>
-          <t>树</t>
+          <t>升起；竖起</t>
         </is>
       </c>
       <c r="E767" s="1" t="inlineStr">
@@ -24915,7 +25043,7 @@
       </c>
       <c r="B770" s="1" t="inlineStr">
         <is>
-          <t>[ˈpio] 推特&lt;名&gt;</t>
+          <t>[/ˈpio/] （鸟的）啾啾声；叽叽声&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C770" s="1" t="inlineStr">
@@ -24925,7 +25053,7 @@
       </c>
       <c r="D770" s="1" t="inlineStr">
         <is>
-          <t>推特</t>
+          <t>（鸟的）啾啾声；叽叽声</t>
         </is>
       </c>
       <c r="E770" s="1" t="inlineStr">
@@ -24950,7 +25078,11 @@
           <t>抄送&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C771" s="1" t="inlineStr"/>
+      <c r="C771" s="1" t="inlineStr">
+        <is>
+          <t>/ˈkopja/</t>
+        </is>
+      </c>
       <c r="D771" s="1" t="inlineStr">
         <is>
           <t>抄送</t>
@@ -25775,7 +25907,7 @@
       </c>
       <c r="B797" s="1" t="inlineStr">
         <is>
-          <t>[baˈɾaxa] 甲板&lt;名&gt;</t>
+          <t>[/baˈɾaxa/] 一副纸牌；纸牌&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C797" s="1" t="inlineStr">
@@ -25785,7 +25917,7 @@
       </c>
       <c r="D797" s="1" t="inlineStr">
         <is>
-          <t>甲板</t>
+          <t>一副纸牌；纸牌</t>
         </is>
       </c>
       <c r="E797" s="1" t="inlineStr">
@@ -26191,7 +26323,7 @@
       </c>
       <c r="B810" s="1" t="inlineStr">
         <is>
-          <t>[fɾeˈɡaɾ] 磨砂膏&lt;动&gt;</t>
+          <t>[/fɾeˈɡaɾ/] 擦洗；刷洗&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C810" s="1" t="inlineStr">
@@ -26201,7 +26333,7 @@
       </c>
       <c r="D810" s="1" t="inlineStr">
         <is>
-          <t>磨砂膏</t>
+          <t>擦洗；刷洗</t>
         </is>
       </c>
       <c r="E810" s="1" t="inlineStr">
@@ -27759,7 +27891,7 @@
       </c>
       <c r="B859" s="1" t="inlineStr">
         <is>
-          <t>[abeθiˈnaɾ] 织布机&lt;动&gt;</t>
+          <t>[/abeθiˈnaɾ/] 临近；逼近&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C859" s="1" t="inlineStr">
@@ -27769,7 +27901,7 @@
       </c>
       <c r="D859" s="1" t="inlineStr">
         <is>
-          <t>织布机</t>
+          <t>临近；逼近</t>
         </is>
       </c>
       <c r="E859" s="1" t="inlineStr">
@@ -27887,7 +28019,7 @@
       </c>
       <c r="B863" s="1" t="inlineStr">
         <is>
-          <t>[ˈʝin] 阴&lt;名&gt;</t>
+          <t>[/ˈʝin/] 阴&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C863" s="1" t="inlineStr">
@@ -27919,7 +28051,7 @@
       </c>
       <c r="B864" s="1" t="inlineStr">
         <is>
-          <t>[ˈfausto] 浮士德&lt;形&gt;</t>
+          <t>[/ˈfausto/] 快乐的；盛大的；吉祥的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C864" s="1" t="inlineStr">
@@ -27929,7 +28061,7 @@
       </c>
       <c r="D864" s="1" t="inlineStr">
         <is>
-          <t>浮士德</t>
+          <t>快乐的；盛大的；吉祥的</t>
         </is>
       </c>
       <c r="E864" s="1" t="inlineStr">
@@ -28367,7 +28499,7 @@
       </c>
       <c r="B878" s="1" t="inlineStr">
         <is>
-          <t>[koˈrida] 射液&lt;名&gt;</t>
+          <t>[/koˈrida/] 奔跑；赛跑；斗牛&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C878" s="1" t="inlineStr">
@@ -28377,7 +28509,7 @@
       </c>
       <c r="D878" s="1" t="inlineStr">
         <is>
-          <t>射液</t>
+          <t>奔跑；赛跑；斗牛</t>
         </is>
       </c>
       <c r="E878" s="1" t="inlineStr">
@@ -28399,7 +28531,7 @@
       </c>
       <c r="B879" s="1" t="inlineStr">
         <is>
-          <t>[inkoˈmodo] 不舒服&lt;名&gt;</t>
+          <t>[/inkoˈmodo/] incómodo：不舒服的（incomodo 为动词 incomodar 的第一人称变位）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C879" s="1" t="inlineStr">
@@ -28409,7 +28541,7 @@
       </c>
       <c r="D879" s="1" t="inlineStr">
         <is>
-          <t>不舒服</t>
+          <t>incómodo：不舒服的（incomodo 为动词 incomodar 的第一人称变位）</t>
         </is>
       </c>
       <c r="E879" s="1" t="inlineStr">
@@ -28751,7 +28883,7 @@
       </c>
       <c r="B890" s="1" t="inlineStr">
         <is>
-          <t>[ˈpaɾti] 聚会&lt;名&gt;</t>
+          <t>[/ˈpaɾti/] （英语借词）聚会，派对&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C890" s="1" t="inlineStr">
@@ -28761,7 +28893,7 @@
       </c>
       <c r="D890" s="1" t="inlineStr">
         <is>
-          <t>聚会</t>
+          <t>（英语借词）聚会，派对&lt;名&gt;</t>
         </is>
       </c>
       <c r="E890" s="1" t="inlineStr">
@@ -28850,7 +28982,11 @@
           <t>自毁&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C893" s="1" t="inlineStr"/>
+      <c r="C893" s="1" t="inlineStr">
+        <is>
+          <t>/autodestɾukθiˈon/</t>
+        </is>
+      </c>
       <c r="D893" s="1" t="inlineStr">
         <is>
           <t>自毁</t>
@@ -28875,7 +29011,7 @@
       </c>
       <c r="B894" s="1" t="inlineStr">
         <is>
-          <t>[ˈaʝo] 阿约&lt;名&gt;</t>
+          <t>[/ˈaʝo/] 家庭教师；保姆&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C894" s="1" t="inlineStr">
@@ -28885,7 +29021,7 @@
       </c>
       <c r="D894" s="1" t="inlineStr">
         <is>
-          <t>阿约</t>
+          <t>家庭教师；保姆</t>
         </is>
       </c>
       <c r="E894" s="1" t="inlineStr">
@@ -29099,7 +29235,7 @@
       </c>
       <c r="B901" s="1" t="inlineStr">
         <is>
-          <t>[dixeˈɾiɾ] 摘要&lt;动&gt;</t>
+          <t>[/dixeˈɾiɾ/] 消化；领会&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C901" s="1" t="inlineStr">
@@ -29109,7 +29245,7 @@
       </c>
       <c r="D901" s="1" t="inlineStr">
         <is>
-          <t>摘要</t>
+          <t>消化；领会</t>
         </is>
       </c>
       <c r="E901" s="1" t="inlineStr">
@@ -29291,7 +29427,7 @@
       </c>
       <c r="B907" s="1" t="inlineStr">
         <is>
-          <t>[baˈrote] 酒吧&lt;名&gt;</t>
+          <t>[/baˈrote/] 横梁；栅栏&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C907" s="1" t="inlineStr">
@@ -29301,7 +29437,7 @@
       </c>
       <c r="D907" s="1" t="inlineStr">
         <is>
-          <t>酒吧</t>
+          <t>横梁；栅栏</t>
         </is>
       </c>
       <c r="E907" s="1" t="inlineStr">
@@ -29515,7 +29651,7 @@
       </c>
       <c r="B914" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɾeθes] 你成长&lt;名&gt;</t>
+          <t>[/ˈkɾeθes/] crecer的第二人称单数现在时（你成长/增长）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C914" s="1" t="inlineStr">
@@ -29525,7 +29661,7 @@
       </c>
       <c r="D914" s="1" t="inlineStr">
         <is>
-          <t>你成长</t>
+          <t>crecer的第二人称单数现在时（你成长/增长）</t>
         </is>
       </c>
       <c r="E914" s="1" t="inlineStr">
@@ -29579,7 +29715,7 @@
       </c>
       <c r="B916" s="1" t="inlineStr">
         <is>
-          <t>[tuˈɾistiko] 游客&lt;形&gt;</t>
+          <t>[/tuˈɾistiko/] 旅游的；观光的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C916" s="1" t="inlineStr">
@@ -29589,7 +29725,7 @@
       </c>
       <c r="D916" s="1" t="inlineStr">
         <is>
-          <t>游客</t>
+          <t>旅游的；观光的</t>
         </is>
       </c>
       <c r="E916" s="1" t="inlineStr">
@@ -29707,7 +29843,7 @@
       </c>
       <c r="B920" s="1" t="inlineStr">
         <is>
-          <t>[salˈdaɾ] 得到回报&lt;动&gt;</t>
+          <t>[/salˈdaɾ/] 结清；清偿&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C920" s="1" t="inlineStr">
@@ -29717,7 +29853,7 @@
       </c>
       <c r="D920" s="1" t="inlineStr">
         <is>
-          <t>得到回报</t>
+          <t>结清；清偿</t>
         </is>
       </c>
       <c r="E920" s="1" t="inlineStr">
@@ -29963,7 +30099,7 @@
       </c>
       <c r="B928" s="1" t="inlineStr">
         <is>
-          <t>[benˈtuɾa] 文图拉&lt;名&gt;</t>
+          <t>[/benˈtuɾa/] 幸运；福气&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C928" s="1" t="inlineStr">
@@ -29973,7 +30109,7 @@
       </c>
       <c r="D928" s="1" t="inlineStr">
         <is>
-          <t>文图拉</t>
+          <t>幸运；福气</t>
         </is>
       </c>
       <c r="E928" s="1" t="inlineStr">
@@ -30059,7 +30195,7 @@
       </c>
       <c r="B931" s="1" t="inlineStr">
         <is>
-          <t>[ˈeʝe] 艾丽&lt;名&gt;</t>
+          <t>[/ˈeʝe/] 字母ll的名称&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C931" s="1" t="inlineStr">
@@ -30069,7 +30205,7 @@
       </c>
       <c r="D931" s="1" t="inlineStr">
         <is>
-          <t>艾丽</t>
+          <t>字母ll的名称</t>
         </is>
       </c>
       <c r="E931" s="1" t="inlineStr">
@@ -30091,7 +30227,7 @@
       </c>
       <c r="B932" s="1" t="inlineStr">
         <is>
-          <t>[kaskaˈbel] 响尾蛇&lt;名&gt;</t>
+          <t>[/kaskaˈbel/] 铃铛，小铃&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C932" s="1" t="inlineStr">
@@ -30101,7 +30237,7 @@
       </c>
       <c r="D932" s="1" t="inlineStr">
         <is>
-          <t>响尾蛇</t>
+          <t>铃铛，小铃&lt;名&gt;</t>
         </is>
       </c>
       <c r="E932" s="1" t="inlineStr">
@@ -30123,7 +30259,7 @@
       </c>
       <c r="B933" s="1" t="inlineStr">
         <is>
-          <t>[deramaˈmjento] 泄漏&lt;名&gt;</t>
+          <t>[/deramaˈmjento/] 洒出，溢出；流淌，流出（如流血、流泪）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C933" s="1" t="inlineStr">
@@ -30133,7 +30269,7 @@
       </c>
       <c r="D933" s="1" t="inlineStr">
         <is>
-          <t>泄漏</t>
+          <t>洒出，溢出；流淌，流出（如流血、流泪）</t>
         </is>
       </c>
       <c r="E933" s="1" t="inlineStr">
@@ -30379,13 +30515,17 @@
       </c>
       <c r="B941" s="1" t="inlineStr">
         <is>
-          <t>硬&lt;形&gt;</t>
-        </is>
-      </c>
-      <c r="C941" s="1" t="inlineStr"/>
+          <t>[[ˈxaɾd] 硬的；坚硬的&lt;adj&gt;</t>
+        </is>
+      </c>
+      <c r="C941" s="1" t="inlineStr">
+        <is>
+          <t>/ˈaɾd/</t>
+        </is>
+      </c>
       <c r="D941" s="1" t="inlineStr">
         <is>
-          <t>硬</t>
+          <t>硬的；坚硬的</t>
         </is>
       </c>
       <c r="E941" s="1" t="inlineStr">
@@ -30858,7 +30998,11 @@
           <t>超声波&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C956" s="1" t="inlineStr"/>
+      <c r="C956" s="1" t="inlineStr">
+        <is>
+          <t>/ekoɣɾaˈfia/</t>
+        </is>
+      </c>
       <c r="D956" s="1" t="inlineStr">
         <is>
           <t>超声波</t>
@@ -31430,7 +31574,11 @@
           <t>反之亦然&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C974" s="1" t="inlineStr"/>
+      <c r="C974" s="1" t="inlineStr">
+        <is>
+          <t>/biseˈbeɾsa/</t>
+        </is>
+      </c>
       <c r="D974" s="1" t="inlineStr">
         <is>
           <t>反之亦然</t>
@@ -31487,7 +31635,7 @@
       </c>
       <c r="B976" s="1" t="inlineStr">
         <is>
-          <t>[ˈpoɾte] 轴承&lt;名&gt;</t>
+          <t>[/ˈpoɾte/] 举止；仪态&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C976" s="1" t="inlineStr">
@@ -31497,7 +31645,7 @@
       </c>
       <c r="D976" s="1" t="inlineStr">
         <is>
-          <t>轴承</t>
+          <t>举止；仪态</t>
         </is>
       </c>
       <c r="E976" s="1" t="inlineStr">
@@ -31679,7 +31827,7 @@
       </c>
       <c r="B982" s="1" t="inlineStr">
         <is>
-          <t>[pɾobiˈdenθja] 普罗维登斯&lt;名&gt;</t>
+          <t>[/pɾobiˈdenθja/] 天意；天命；规定&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C982" s="1" t="inlineStr">
@@ -31689,7 +31837,7 @@
       </c>
       <c r="D982" s="1" t="inlineStr">
         <is>
-          <t>普罗维登斯</t>
+          <t>天意；天命；规定</t>
         </is>
       </c>
       <c r="E982" s="1" t="inlineStr">
@@ -31842,7 +31990,11 @@
           <t>站。&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C987" s="1" t="inlineStr"/>
+      <c r="C987" s="1" t="inlineStr">
+        <is>
+          <t>/ˈsanta/</t>
+        </is>
+      </c>
       <c r="D987" s="1" t="inlineStr">
         <is>
           <t>站。</t>
@@ -31899,7 +32051,7 @@
       </c>
       <c r="B989" s="1" t="inlineStr">
         <is>
-          <t>[liˈbjano] 光&lt;名&gt;</t>
+          <t>[/liˈbjano/] 轻的；轻便的；轻微的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C989" s="1" t="inlineStr">
@@ -31909,7 +32061,7 @@
       </c>
       <c r="D989" s="1" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>轻的；轻便的；轻微的</t>
         </is>
       </c>
       <c r="E989" s="1" t="inlineStr">
@@ -32318,7 +32470,11 @@
           <t>点击&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1002" s="1" t="inlineStr"/>
+      <c r="C1002" s="1" t="inlineStr">
+        <is>
+          <t>/tˈap/</t>
+        </is>
+      </c>
       <c r="D1002" s="1" t="inlineStr">
         <is>
           <t>点击</t>
@@ -32439,7 +32595,7 @@
       </c>
       <c r="B1006" s="1" t="inlineStr">
         <is>
-          <t>[ˈnuɲo] 努诺&lt;名&gt;</t>
+          <t>[/ˈnuɲo/] （西语中无此常用词；仅作专有名词Nuño）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1006" s="1" t="inlineStr">
@@ -32449,7 +32605,7 @@
       </c>
       <c r="D1006" s="1" t="inlineStr">
         <is>
-          <t>努诺</t>
+          <t>（西语中无此常用词；仅作专有名词Nuño）</t>
         </is>
       </c>
       <c r="E1006" s="1" t="inlineStr">
@@ -32535,7 +32691,7 @@
       </c>
       <c r="B1009" s="1" t="inlineStr">
         <is>
-          <t>[soɾˈteo] 画&lt;名&gt;</t>
+          <t>[/soɾˈteo/] 抽签；抽奖；抽彩&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1009" s="1" t="inlineStr">
@@ -32545,7 +32701,7 @@
       </c>
       <c r="D1009" s="1" t="inlineStr">
         <is>
-          <t>画</t>
+          <t>抽签；抽奖；抽彩</t>
         </is>
       </c>
       <c r="E1009" s="1" t="inlineStr">
@@ -32570,7 +32726,11 @@
           <t>偶尔的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1010" s="1" t="inlineStr"/>
+      <c r="C1010" s="1" t="inlineStr">
+        <is>
+          <t>/okasjoˈnal/</t>
+        </is>
+      </c>
       <c r="D1010" s="1" t="inlineStr">
         <is>
           <t>偶尔的</t>
@@ -32595,7 +32755,7 @@
       </c>
       <c r="B1011" s="1" t="inlineStr">
         <is>
-          <t>[repɾoduˈθiɾ] 玩&lt;动&gt;</t>
+          <t>[/repɾoduˈθiɾ/] 复制；繁殖；播放&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1011" s="1" t="inlineStr">
@@ -32605,7 +32765,7 @@
       </c>
       <c r="D1011" s="1" t="inlineStr">
         <is>
-          <t>玩</t>
+          <t>复制；繁殖；播放</t>
         </is>
       </c>
       <c r="E1011" s="1" t="inlineStr">
@@ -32723,7 +32883,7 @@
       </c>
       <c r="B1015" s="1" t="inlineStr">
         <is>
-          <t>[ˈro] 罗&lt;名&gt;</t>
+          <t>[/ˈro/] （西语中无此词；字母r的名称为erre）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1015" s="1" t="inlineStr">
@@ -32733,7 +32893,7 @@
       </c>
       <c r="D1015" s="1" t="inlineStr">
         <is>
-          <t>罗</t>
+          <t>（西语中无此词；字母r的名称为erre）</t>
         </is>
       </c>
       <c r="E1015" s="1" t="inlineStr">
@@ -32886,7 +33046,11 @@
           <t>毒理学的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1020" s="1" t="inlineStr"/>
+      <c r="C1020" s="1" t="inlineStr">
+        <is>
+          <t>/toksikoˈloxiko/</t>
+        </is>
+      </c>
       <c r="D1020" s="1" t="inlineStr">
         <is>
           <t>毒理学的</t>
@@ -32975,7 +33139,7 @@
       </c>
       <c r="B1023" s="1" t="inlineStr">
         <is>
-          <t>[paˈtɾiθjo] 帕特里克&lt;名&gt;</t>
+          <t>[/paˈtɾiθjo/] 贵族；贵族的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1023" s="1" t="inlineStr">
@@ -32985,7 +33149,7 @@
       </c>
       <c r="D1023" s="1" t="inlineStr">
         <is>
-          <t>帕特里克</t>
+          <t>贵族；贵族的</t>
         </is>
       </c>
       <c r="E1023" s="1" t="inlineStr">
@@ -33071,7 +33235,7 @@
       </c>
       <c r="B1026" s="1" t="inlineStr">
         <is>
-          <t>[aɡoˈtaɾ] 排气&lt;动&gt;</t>
+          <t>[/aɡoˈtaɾ/] 耗尽；用尽；使筋疲力尽&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1026" s="1" t="inlineStr">
@@ -33081,7 +33245,7 @@
       </c>
       <c r="D1026" s="1" t="inlineStr">
         <is>
-          <t>排气</t>
+          <t>耗尽；用尽；使筋疲力尽</t>
         </is>
       </c>
       <c r="E1026" s="1" t="inlineStr">
@@ -33103,7 +33267,7 @@
       </c>
       <c r="B1027" s="1" t="inlineStr">
         <is>
-          <t>[planteˈaɾ] 姿势&lt;动&gt;</t>
+          <t>[/planteˈaɾ/] 提出；拟定&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1027" s="1" t="inlineStr">
@@ -33113,7 +33277,7 @@
       </c>
       <c r="D1027" s="1" t="inlineStr">
         <is>
-          <t>姿势</t>
+          <t>提出；拟定</t>
         </is>
       </c>
       <c r="E1027" s="1" t="inlineStr">
@@ -33135,7 +33299,7 @@
       </c>
       <c r="B1028" s="1" t="inlineStr">
         <is>
-          <t>[lumiˈnoso] 发光的&lt;形&gt;</t>
+          <t>[/lumiˈnoso/] 明亮的；光亮的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1028" s="1" t="inlineStr">
@@ -33145,7 +33309,7 @@
       </c>
       <c r="D1028" s="1" t="inlineStr">
         <is>
-          <t>发光的</t>
+          <t>明亮的；光亮的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1028" s="1" t="inlineStr">
@@ -33618,7 +33782,11 @@
           <t>渡轮&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1043" s="1" t="inlineStr"/>
+      <c r="C1043" s="1" t="inlineStr">
+        <is>
+          <t>/tɾasboɾdadˈoɾ/</t>
+        </is>
+      </c>
       <c r="D1043" s="1" t="inlineStr">
         <is>
           <t>渡轮</t>
@@ -33870,7 +34038,11 @@
           <t>去&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C1051" s="1" t="inlineStr"/>
+      <c r="C1051" s="1" t="inlineStr">
+        <is>
+          <t>/ʝˈendo/</t>
+        </is>
+      </c>
       <c r="D1051" s="1" t="inlineStr">
         <is>
           <t>去</t>
@@ -33930,7 +34102,11 @@
           <t>[beˈbe] 幼童；宝贝；BB弹&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1053" s="1" t="inlineStr"/>
+      <c r="C1053" s="1" t="inlineStr">
+        <is>
+          <t>/beˈbe/</t>
+        </is>
+      </c>
       <c r="D1053" s="1" t="inlineStr">
         <is>
           <t>幼童</t>
@@ -33987,7 +34163,7 @@
       </c>
       <c r="B1055" s="1" t="inlineStr">
         <is>
-          <t>[bateˈaɾ] 蝙蝠&lt;动&gt;</t>
+          <t>[/bateˈaɾ/] （棒球）击球&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1055" s="1" t="inlineStr">
@@ -33997,7 +34173,7 @@
       </c>
       <c r="D1055" s="1" t="inlineStr">
         <is>
-          <t>蝙蝠</t>
+          <t>（棒球）击球</t>
         </is>
       </c>
       <c r="E1055" s="1" t="inlineStr">
@@ -34374,7 +34550,11 @@
           <t>正方形&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1067" s="1" t="inlineStr"/>
+      <c r="C1067" s="1" t="inlineStr">
+        <is>
+          <t>/kwaˈdɾaða/</t>
+        </is>
+      </c>
       <c r="D1067" s="1" t="inlineStr">
         <is>
           <t>正方形</t>
@@ -34399,7 +34579,7 @@
       </c>
       <c r="B1068" s="1" t="inlineStr">
         <is>
-          <t>[laˈdɾaɾ] 树皮&lt;动&gt;</t>
+          <t>[/laˈdɾaɾ/] （狗）吠叫&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1068" s="1" t="inlineStr">
@@ -34409,7 +34589,7 @@
       </c>
       <c r="D1068" s="1" t="inlineStr">
         <is>
-          <t>树皮</t>
+          <t>（狗）吠叫</t>
         </is>
       </c>
       <c r="E1068" s="1" t="inlineStr">
@@ -34434,7 +34614,11 @@
           <t>放纵的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1069" s="1" t="inlineStr"/>
+      <c r="C1069" s="1" t="inlineStr">
+        <is>
+          <t>/indulˈxente/</t>
+        </is>
+      </c>
       <c r="D1069" s="1" t="inlineStr">
         <is>
           <t>放纵的</t>
@@ -34779,7 +34963,7 @@
       </c>
       <c r="B1080" s="1" t="inlineStr">
         <is>
-          <t>[toˈpaɾ] 凹凸&lt;动&gt;</t>
+          <t>[/toˈpaɾ/] 碰撞；撞上；偶遇&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1080" s="1" t="inlineStr">
@@ -34789,7 +34973,7 @@
       </c>
       <c r="D1080" s="1" t="inlineStr">
         <is>
-          <t>凹凸</t>
+          <t>碰撞；撞上；偶遇</t>
         </is>
       </c>
       <c r="E1080" s="1" t="inlineStr">
@@ -34971,7 +35155,7 @@
       </c>
       <c r="B1086" s="1" t="inlineStr">
         <is>
-          <t>[ˈlof] 阁楼&lt;名&gt;</t>
+          <t>[/ˈlof/] 大开间公寓；阁楼式住宅&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1086" s="1" t="inlineStr">
@@ -34981,7 +35165,7 @@
       </c>
       <c r="D1086" s="1" t="inlineStr">
         <is>
-          <t>阁楼</t>
+          <t>大开间公寓；阁楼式住宅&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1086" s="1" t="inlineStr">
@@ -35006,7 +35190,11 @@
           <t>令人兴奋的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1087" s="1" t="inlineStr"/>
+      <c r="C1087" s="1" t="inlineStr">
+        <is>
+          <t>/apasjoˈnante/</t>
+        </is>
+      </c>
       <c r="D1087" s="1" t="inlineStr">
         <is>
           <t>令人兴奋的</t>
@@ -35031,7 +35219,7 @@
       </c>
       <c r="B1088" s="1" t="inlineStr">
         <is>
-          <t>[koˈlado] 紧张的&lt;形&gt;</t>
+          <t>[/koˈlado/] 过滤的；迷恋的；不速之客&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1088" s="1" t="inlineStr">
@@ -35041,7 +35229,7 @@
       </c>
       <c r="D1088" s="1" t="inlineStr">
         <is>
-          <t>紧张的</t>
+          <t>过滤的；迷恋的；不速之客</t>
         </is>
       </c>
       <c r="E1088" s="1" t="inlineStr">
@@ -35159,7 +35347,7 @@
       </c>
       <c r="B1092" s="1" t="inlineStr">
         <is>
-          <t>[kaɾmiˈnaɾ] 胭脂红&lt;动&gt;</t>
+          <t>[/kaɾmiˈnaɾ/] 染成胭脂红色；使变红&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1092" s="1" t="inlineStr">
@@ -35169,7 +35357,7 @@
       </c>
       <c r="D1092" s="1" t="inlineStr">
         <is>
-          <t>胭脂红</t>
+          <t>染成胭脂红色；使变红</t>
         </is>
       </c>
       <c r="E1092" s="1" t="inlineStr">
@@ -35191,7 +35379,7 @@
       </c>
       <c r="B1093" s="1" t="inlineStr">
         <is>
-          <t>[loˈkeɾo] 收缩&lt;名&gt;</t>
+          <t>[/loˈkeɾo/] （西语中无此常用词）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1093" s="1" t="inlineStr">
@@ -35201,7 +35389,7 @@
       </c>
       <c r="D1093" s="1" t="inlineStr">
         <is>
-          <t>收缩</t>
+          <t>（西语中无此常用词）</t>
         </is>
       </c>
       <c r="E1093" s="1" t="inlineStr">
@@ -35354,7 +35542,11 @@
           <t>微笑&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C1098" s="1" t="inlineStr"/>
+      <c r="C1098" s="1" t="inlineStr">
+        <is>
+          <t>/sonɾeˈiɾ/</t>
+        </is>
+      </c>
       <c r="D1098" s="1" t="inlineStr">
         <is>
           <t>微笑</t>
